--- a/deliverables/26-27_On_Call_Schedule_v1_minimal_repair.xlsx
+++ b/deliverables/26-27_On_Call_Schedule_v1_minimal_repair.xlsx
@@ -2664,31 +2664,31 @@
       <c r="AG6" s="205" t="n"/>
       <c r="AH6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AI6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AJ6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AL6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AM6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AN6" s="92">
         <f>SUM(AH6:AM6)</f>
-        <v/>
+        <v>28</v>
       </c>
     </row>
     <row r="7" ht="9.949999999999999" customHeight="1">
@@ -2872,35 +2872,35 @@
       <c r="AG9" s="205" t="n"/>
       <c r="AH9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AI9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AJ9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AK9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AM9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AN9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AO9" s="92">
         <f>SUM(AH9:AN9)</f>
-        <v/>
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -3083,23 +3083,23 @@
       <c r="AG12" s="205" t="n"/>
       <c r="AH12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AJ12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AL12" s="84">
         <f>SUM(AH12:AK12)</f>
-        <v/>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -4137,23 +4137,23 @@
       </c>
       <c r="E38" s="104">
         <f>COUNTIF($E$5:$H$21,"*Hard*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F38" s="104">
         <f>COUNTIF($I$5:$N$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G38" s="104">
         <f>COUNTIF($O$5:$V$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H38" s="104">
         <f>COUNTIF($C$5:$D$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I38" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -4164,23 +4164,23 @@
       </c>
       <c r="E39" s="104">
         <f>COUNTIF($E$5:$H$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F39" s="104">
         <f>COUNTIF($I$5:$N$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G39" s="104">
         <f>COUNTIF($O$5:$V$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H39" s="104">
         <f>COUNTIF($C$5:$D$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I39" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -4191,23 +4191,23 @@
       </c>
       <c r="E40" s="104">
         <f>COUNTIF($E$5:$H$21,"*Schutt*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F40" s="104">
         <f>COUNTIF($I$5:$N$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G40" s="104">
         <f>COUNTIF($O$5:$V$21,"*Schutt*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="H40" s="104">
         <f>COUNTIF($C$5:$D$21,"*Schutt*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I40" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -4218,23 +4218,23 @@
       </c>
       <c r="E41" s="104">
         <f>COUNTIF($E$5:$H$21,"*Stanek*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F41" s="104">
         <f>COUNTIF($I$5:$N$21,"*Stanek*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G41" s="104">
         <f>COUNTIF($O$5:$V$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H41" s="104">
         <f>COUNTIF($C$5:$D$21,"*Stanek*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I41" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -4245,23 +4245,23 @@
       </c>
       <c r="E42" s="104">
         <f>COUNTIF($E$5:$H$21,"*Strand*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F42" s="104">
         <f>COUNTIF($I$5:$N$21,"*Strand*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G42" s="104">
         <f>COUNTIF($O$5:$V$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H42" s="104">
         <f>COUNTIF($C$5:$D$21,"*Strand*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I42" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -4272,23 +4272,23 @@
       </c>
       <c r="E43" s="104">
         <f>COUNTIF($E$5:$H$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F43" s="104">
         <f>COUNTIF($I$5:$N$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="G43" s="104">
         <f>COUNTIF($O$5:$V$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H43" s="104">
         <f>COUNTIF($C$5:$D$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I43" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -4307,23 +4307,23 @@
       </c>
       <c r="E45" s="106">
         <f>COUNTIF($E$5:$H$21,"*Beutel*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F45" s="106">
         <f>COUNTIF($I$5:$N$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G45" s="106">
         <f>COUNTIF($O$5:$V$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H45" s="106">
         <f>COUNTIF($C$5:$D$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I45" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4334,23 +4334,23 @@
       </c>
       <c r="E46" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F46" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bottke*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G46" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H46" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I46" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -4361,23 +4361,23 @@
       </c>
       <c r="E47" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F47" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G47" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H47" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I47" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4388,23 +4388,23 @@
       </c>
       <c r="E48" s="106">
         <f>COUNTIF($E$5:$H$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F48" s="106">
         <f>COUNTIF($I$5:$N$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G48" s="106">
         <f>COUNTIF($O$5:$V$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H48" s="106">
         <f>COUNTIF($C$5:$D$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I48" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4415,23 +4415,23 @@
       </c>
       <c r="E49" s="106">
         <f>COUNTIF($E$5:$H$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F49" s="106">
         <f>COUNTIF($I$5:$N$21,"*Kendrick*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G49" s="106">
         <f>COUNTIF($O$5:$V$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H49" s="106">
         <f>COUNTIF($C$5:$D$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I49" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -4442,23 +4442,23 @@
       </c>
       <c r="E50" s="106">
         <f>COUNTIF($E$5:$H$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F50" s="106">
         <f>COUNTIF($I$5:$N$21,"*Patel*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G50" s="106">
         <f>COUNTIF($O$5:$V$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H50" s="106">
         <f>COUNTIF($C$5:$D$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I50" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4469,23 +4469,23 @@
       </c>
       <c r="E51" s="106">
         <f>COUNTIF($E$5:$H$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F51" s="106">
         <f>COUNTIF($I$5:$N$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G51" s="106">
         <f>COUNTIF($O$5:$V$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H51" s="106">
         <f>COUNTIF($C$5:$D$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I51" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4504,23 +4504,23 @@
       </c>
       <c r="E53" s="107">
         <f>COUNTIF($E$5:$H$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F53" s="107">
         <f>COUNTIF($I$5:$N$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G53" s="107">
         <f>COUNTIF($O$5:$V$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H53" s="107">
         <f>COUNTIF($C$5:$D$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I53" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4531,23 +4531,23 @@
       </c>
       <c r="E54" s="107">
         <f>COUNTIF($E$5:$H$21,"*Lux*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F54" s="107">
         <f>COUNTIF($I$5:$N$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G54" s="107">
         <f>COUNTIF($O$5:$V$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H54" s="107">
         <f>COUNTIF($C$5:$D$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I54" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -4558,23 +4558,23 @@
       </c>
       <c r="E55" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mautino*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F55" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G55" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mautino*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="H55" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I55" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -4585,45 +4585,45 @@
       </c>
       <c r="E56" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F56" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mudondo*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G56" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H56" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I56" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="E57" s="95">
         <f>SUM(E38:E56)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="F57" s="95">
         <f>SUM(F38:F56)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="G57" s="95">
         <f>SUM(G38:G56)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="H57" s="95">
         <f>SUM(H38:H56)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="I57" s="95">
         <f>SUM(I38:I56)</f>
-        <v/>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5066,31 +5066,31 @@
       <c r="AG6" s="205" t="n"/>
       <c r="AH6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AJ6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AK6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AN6" s="92">
         <f>SUM(AH6:AM6)</f>
-        <v/>
+        <v>31</v>
       </c>
     </row>
     <row r="7" ht="9.949999999999999" customHeight="1">
@@ -5275,35 +5275,35 @@
       <c r="AG9" s="205" t="n"/>
       <c r="AH9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AI9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AJ9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AL9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AM9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AN9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AO9" s="92">
         <f>SUM(AH9:AN9)</f>
-        <v/>
+        <v>16</v>
       </c>
     </row>
     <row r="10" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -5487,23 +5487,23 @@
       <c r="AG12" s="205" t="n"/>
       <c r="AH12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AI12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AJ12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AK12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL12" s="84">
         <f>SUM(AH12:AK12)</f>
-        <v/>
+        <v>15</v>
       </c>
     </row>
     <row r="13" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -6542,23 +6542,23 @@
       </c>
       <c r="E38" s="104">
         <f>COUNTIF($E$5:$H$21,"*Hard*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F38" s="104">
         <f>COUNTIF($I$5:$N$21,"*Hard*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="G38" s="104">
         <f>COUNTIF($O$5:$V$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H38" s="104">
         <f>COUNTIF($C$5:$D$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I38" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -6569,23 +6569,23 @@
       </c>
       <c r="E39" s="104">
         <f>COUNTIF($E$5:$H$21,"*Oehm*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F39" s="104">
         <f>COUNTIF($I$5:$N$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G39" s="104">
         <f>COUNTIF($O$5:$V$21,"*Oehm*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="H39" s="104">
         <f>COUNTIF($C$5:$D$21,"*Oehm*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I39" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -6596,23 +6596,23 @@
       </c>
       <c r="E40" s="104">
         <f>COUNTIF($E$5:$H$21,"*Schutt*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F40" s="104">
         <f>COUNTIF($I$5:$N$21,"*Schutt*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G40" s="104">
         <f>COUNTIF($O$5:$V$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H40" s="104">
         <f>COUNTIF($C$5:$D$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I40" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -6623,23 +6623,23 @@
       </c>
       <c r="E41" s="104">
         <f>COUNTIF($E$5:$H$21,"*Stanek*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F41" s="104">
         <f>COUNTIF($I$5:$N$21,"*Stanek*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G41" s="104">
         <f>COUNTIF($O$5:$V$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H41" s="104">
         <f>COUNTIF($C$5:$D$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I41" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -6650,23 +6650,23 @@
       </c>
       <c r="E42" s="104">
         <f>COUNTIF($E$5:$H$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F42" s="104">
         <f>COUNTIF($I$5:$N$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G42" s="104">
         <f>COUNTIF($O$5:$V$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H42" s="104">
         <f>COUNTIF($C$5:$D$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I42" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -6677,23 +6677,23 @@
       </c>
       <c r="E43" s="104">
         <f>COUNTIF($E$5:$H$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F43" s="104">
         <f>COUNTIF($I$5:$N$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="G43" s="104">
         <f>COUNTIF($O$5:$V$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H43" s="104">
         <f>COUNTIF($C$5:$D$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="I43" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -6712,23 +6712,23 @@
       </c>
       <c r="E45" s="106">
         <f>COUNTIF($E$5:$H$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F45" s="106">
         <f>COUNTIF($I$5:$N$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G45" s="106">
         <f>COUNTIF($O$5:$V$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H45" s="106">
         <f>COUNTIF($C$5:$D$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I45" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -6739,23 +6739,23 @@
       </c>
       <c r="E46" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F46" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G46" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H46" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I46" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -6766,23 +6766,23 @@
       </c>
       <c r="E47" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F47" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G47" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H47" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I47" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -6793,23 +6793,23 @@
       </c>
       <c r="E48" s="106">
         <f>COUNTIF($E$5:$H$21,"*Gaspar*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F48" s="106">
         <f>COUNTIF($I$5:$N$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G48" s="106">
         <f>COUNTIF($O$5:$V$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H48" s="106">
         <f>COUNTIF($C$5:$D$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I48" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -6820,23 +6820,23 @@
       </c>
       <c r="E49" s="106">
         <f>COUNTIF($E$5:$H$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F49" s="106">
         <f>COUNTIF($I$5:$N$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G49" s="106">
         <f>COUNTIF($O$5:$V$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H49" s="106">
         <f>COUNTIF($C$5:$D$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I49" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -6847,23 +6847,23 @@
       </c>
       <c r="E50" s="106">
         <f>COUNTIF($E$5:$H$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F50" s="106">
         <f>COUNTIF($I$5:$N$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G50" s="106">
         <f>COUNTIF($O$5:$V$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H50" s="106">
         <f>COUNTIF($C$5:$D$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I50" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -6874,23 +6874,23 @@
       </c>
       <c r="E51" s="106">
         <f>COUNTIF($E$5:$H$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F51" s="106">
         <f>COUNTIF($I$5:$N$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G51" s="106">
         <f>COUNTIF($O$5:$V$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H51" s="106">
         <f>COUNTIF($C$5:$D$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I51" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -6909,23 +6909,23 @@
       </c>
       <c r="E53" s="107">
         <f>COUNTIF($E$5:$H$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F53" s="107">
         <f>COUNTIF($I$5:$N$21,"*Johnson*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G53" s="107">
         <f>COUNTIF($O$5:$V$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H53" s="107">
         <f>COUNTIF($C$5:$D$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I53" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -6936,23 +6936,23 @@
       </c>
       <c r="E54" s="107">
         <f>COUNTIF($E$5:$H$21,"*Lux*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F54" s="107">
         <f>COUNTIF($I$5:$N$21,"*Lux*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G54" s="107">
         <f>COUNTIF($O$5:$V$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H54" s="107">
         <f>COUNTIF($C$5:$D$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I54" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -6963,23 +6963,23 @@
       </c>
       <c r="E55" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mautino*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F55" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mautino*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G55" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H55" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I55" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -6990,45 +6990,45 @@
       </c>
       <c r="E56" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mudondo*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F56" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G56" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mudondo*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="H56" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I56" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="E57" s="95">
         <f>SUM(E38:E56)</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="F57" s="95">
         <f>SUM(F38:F56)</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="G57" s="95">
         <f>SUM(G38:G56)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="H57" s="95">
         <f>SUM(H38:H56)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="I57" s="95">
         <f>SUM(I38:I56)</f>
-        <v/>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -7460,31 +7460,31 @@
       <c r="AG6" s="205" t="n"/>
       <c r="AH6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AI6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AJ6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AK6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AL6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AM6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AN6" s="92">
         <f>SUM(AH6:AM6)</f>
-        <v/>
+        <v>30</v>
       </c>
     </row>
     <row r="7" ht="9.949999999999999" customHeight="1">
@@ -7668,35 +7668,35 @@
       <c r="AG9" s="205" t="n"/>
       <c r="AH9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AI9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AJ9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AK9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AL9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AN9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AO9" s="92">
         <f>SUM(AH9:AN9)</f>
-        <v/>
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -7879,23 +7879,23 @@
       <c r="AG12" s="205" t="n"/>
       <c r="AH12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AJ12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AL12" s="84">
         <f>SUM(AH12:AK12)</f>
-        <v/>
+        <v>11</v>
       </c>
     </row>
     <row r="13" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -8963,23 +8963,23 @@
       </c>
       <c r="E38" s="104">
         <f>COUNTIF($E$5:$H$21,"*Hard*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F38" s="104">
         <f>COUNTIF($I$5:$N$21,"*Hard*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G38" s="104">
         <f>COUNTIF($O$5:$V$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H38" s="104">
         <f>COUNTIF($C$5:$D$21,"*Hard*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I38" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -8990,23 +8990,23 @@
       </c>
       <c r="E39" s="104">
         <f>COUNTIF($E$5:$H$21,"*Oehm*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F39" s="104">
         <f>COUNTIF($I$5:$N$21,"*Oehm*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="G39" s="104">
         <f>COUNTIF($O$5:$V$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H39" s="104">
         <f>COUNTIF($C$5:$D$21,"*Oehm*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I39" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -9017,23 +9017,23 @@
       </c>
       <c r="E40" s="104">
         <f>COUNTIF($E$5:$H$21,"*Schutt*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F40" s="104">
         <f>COUNTIF($I$5:$N$21,"*Schutt*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G40" s="104">
         <f>COUNTIF($O$5:$V$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H40" s="104">
         <f>COUNTIF($C$5:$D$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I40" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -9044,23 +9044,23 @@
       </c>
       <c r="E41" s="104">
         <f>COUNTIF($E$5:$H$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F41" s="104">
         <f>COUNTIF($I$5:$N$21,"*Stanek*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="G41" s="104">
         <f>COUNTIF($O$5:$V$21,"*Stanek*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H41" s="104">
         <f>COUNTIF($C$5:$D$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I41" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -9071,23 +9071,23 @@
       </c>
       <c r="E42" s="104">
         <f>COUNTIF($E$5:$H$21,"*Strand*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F42" s="104">
         <f>COUNTIF($I$5:$N$21,"*Strand*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G42" s="104">
         <f>COUNTIF($O$5:$V$21,"*Strand*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="H42" s="104">
         <f>COUNTIF($C$5:$D$21,"*Strand*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I42" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -9098,23 +9098,23 @@
       </c>
       <c r="E43" s="104">
         <f>COUNTIF($E$5:$H$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F43" s="104">
         <f>COUNTIF($I$5:$N$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G43" s="104">
         <f>COUNTIF($O$5:$V$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H43" s="104">
         <f>COUNTIF($C$5:$D$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I43" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -9133,23 +9133,23 @@
       </c>
       <c r="E45" s="106">
         <f>COUNTIF($E$5:$H$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F45" s="106">
         <f>COUNTIF($I$5:$N$21,"*Beutel*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G45" s="106">
         <f>COUNTIF($O$5:$V$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H45" s="106">
         <f>COUNTIF($C$5:$D$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I45" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -9160,23 +9160,23 @@
       </c>
       <c r="E46" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F46" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G46" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H46" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I46" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -9187,23 +9187,23 @@
       </c>
       <c r="E47" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F47" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G47" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H47" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I47" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -9214,23 +9214,23 @@
       </c>
       <c r="E48" s="106">
         <f>COUNTIF($E$5:$H$21,"*Gaspar*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F48" s="106">
         <f>COUNTIF($I$5:$N$21,"*Gaspar*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G48" s="106">
         <f>COUNTIF($O$5:$V$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H48" s="106">
         <f>COUNTIF($C$5:$D$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I48" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -9241,23 +9241,23 @@
       </c>
       <c r="E49" s="106">
         <f>COUNTIF($E$5:$H$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F49" s="106">
         <f>COUNTIF($I$5:$N$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G49" s="106">
         <f>COUNTIF($O$5:$V$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H49" s="106">
         <f>COUNTIF($C$5:$D$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I49" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -9268,23 +9268,23 @@
       </c>
       <c r="E50" s="106">
         <f>COUNTIF($E$5:$H$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F50" s="106">
         <f>COUNTIF($I$5:$N$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G50" s="106">
         <f>COUNTIF($O$5:$V$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H50" s="106">
         <f>COUNTIF($C$5:$D$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I50" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -9295,23 +9295,23 @@
       </c>
       <c r="E51" s="106">
         <f>COUNTIF($E$5:$H$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F51" s="106">
         <f>COUNTIF($I$5:$N$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G51" s="106">
         <f>COUNTIF($O$5:$V$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H51" s="106">
         <f>COUNTIF($C$5:$D$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I51" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -9330,23 +9330,23 @@
       </c>
       <c r="E53" s="107">
         <f>COUNTIF($E$5:$H$21,"*Johnson*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F53" s="107">
         <f>COUNTIF($I$5:$N$21,"*Johnson*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G53" s="107">
         <f>COUNTIF($O$5:$V$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H53" s="107">
         <f>COUNTIF($C$5:$D$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I53" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -9357,23 +9357,23 @@
       </c>
       <c r="E54" s="107">
         <f>COUNTIF($E$5:$H$21,"*Lux*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F54" s="107">
         <f>COUNTIF($I$5:$N$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G54" s="107">
         <f>COUNTIF($O$5:$V$21,"*Lux*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="H54" s="107">
         <f>COUNTIF($C$5:$D$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I54" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -9384,23 +9384,23 @@
       </c>
       <c r="E55" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mautino*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F55" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mautino*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G55" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H55" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I55" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -9411,45 +9411,45 @@
       </c>
       <c r="E56" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mudondo*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F56" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mudondo*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G56" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H56" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I56" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="E57" s="95">
         <f>SUM(E38:E56)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="F57" s="95">
         <f>SUM(F38:F56)</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="G57" s="95">
         <f>SUM(G38:G56)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="H57" s="95">
         <f>SUM(H38:H56)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="I57" s="95">
         <f>SUM(I38:I56)</f>
-        <v/>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -9870,31 +9870,31 @@
       <c r="AG6" s="205" t="n"/>
       <c r="AH6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AJ6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AM6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AN6" s="92">
         <f>SUM(AH6:AM6)</f>
-        <v/>
+        <v>31</v>
       </c>
     </row>
     <row r="7" ht="9.949999999999999" customHeight="1">
@@ -10078,35 +10078,35 @@
       <c r="AG9" s="205" t="n"/>
       <c r="AH9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AI9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AJ9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AK9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AL9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AM9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AN9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AO9" s="92">
         <f>SUM(AH9:AN9)</f>
-        <v/>
+        <v>21</v>
       </c>
     </row>
     <row r="10" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -10289,23 +10289,23 @@
       <c r="AG12" s="205" t="n"/>
       <c r="AH12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AI12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AJ12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AL12" s="84">
         <f>SUM(AH12:AK12)</f>
-        <v/>
+        <v>10</v>
       </c>
     </row>
     <row r="13" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -11376,23 +11376,23 @@
       </c>
       <c r="E38" s="104">
         <f>COUNTIF($E$5:$H$21,"*Hard*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F38" s="104">
         <f>COUNTIF($I$5:$N$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G38" s="104">
         <f>COUNTIF($O$5:$V$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H38" s="104">
         <f>COUNTIF($C$5:$D$21,"*Hard*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I38" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -11403,23 +11403,23 @@
       </c>
       <c r="E39" s="104">
         <f>COUNTIF($E$5:$H$21,"*Oehm*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F39" s="104">
         <f>COUNTIF($I$5:$N$21,"*Oehm*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G39" s="104">
         <f>COUNTIF($O$5:$V$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H39" s="104">
         <f>COUNTIF($C$5:$D$21,"*Oehm*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I39" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -11430,23 +11430,23 @@
       </c>
       <c r="E40" s="104">
         <f>COUNTIF($E$5:$H$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F40" s="104">
         <f>COUNTIF($I$5:$N$21,"*Schutt*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="G40" s="104">
         <f>COUNTIF($O$5:$V$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H40" s="104">
         <f>COUNTIF($C$5:$D$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I40" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -11457,23 +11457,23 @@
       </c>
       <c r="E41" s="104">
         <f>COUNTIF($E$5:$H$21,"*Stanek*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F41" s="104">
         <f>COUNTIF($I$5:$N$21,"*Stanek*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G41" s="104">
         <f>COUNTIF($O$5:$V$21,"*Stanek*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="H41" s="104">
         <f>COUNTIF($C$5:$D$21,"*Stanek*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I41" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -11484,23 +11484,23 @@
       </c>
       <c r="E42" s="104">
         <f>COUNTIF($E$5:$H$21,"*Strand*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F42" s="104">
         <f>COUNTIF($I$5:$N$21,"*Strand*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="G42" s="104">
         <f>COUNTIF($O$5:$V$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H42" s="104">
         <f>COUNTIF($C$5:$D$21,"*Strand*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I42" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -11511,23 +11511,23 @@
       </c>
       <c r="E43" s="104">
         <f>COUNTIF($E$5:$H$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F43" s="104">
         <f>COUNTIF($I$5:$N$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G43" s="104">
         <f>COUNTIF($O$5:$V$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H43" s="104">
         <f>COUNTIF($C$5:$D$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I43" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -11546,23 +11546,23 @@
       </c>
       <c r="E45" s="106">
         <f>COUNTIF($E$5:$H$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F45" s="106">
         <f>COUNTIF($I$5:$N$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G45" s="106">
         <f>COUNTIF($O$5:$V$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H45" s="106">
         <f>COUNTIF($C$5:$D$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I45" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -11573,23 +11573,23 @@
       </c>
       <c r="E46" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F46" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G46" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H46" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I46" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -11600,23 +11600,23 @@
       </c>
       <c r="E47" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F47" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G47" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H47" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I47" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -11627,23 +11627,23 @@
       </c>
       <c r="E48" s="106">
         <f>COUNTIF($E$5:$H$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F48" s="106">
         <f>COUNTIF($I$5:$N$21,"*Gaspar*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G48" s="106">
         <f>COUNTIF($O$5:$V$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H48" s="106">
         <f>COUNTIF($C$5:$D$21,"*Gaspar*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I48" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -11654,23 +11654,23 @@
       </c>
       <c r="E49" s="106">
         <f>COUNTIF($E$5:$H$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F49" s="106">
         <f>COUNTIF($I$5:$N$21,"*Kendrick*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G49" s="106">
         <f>COUNTIF($O$5:$V$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H49" s="106">
         <f>COUNTIF($C$5:$D$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I49" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -11681,23 +11681,23 @@
       </c>
       <c r="E50" s="106">
         <f>COUNTIF($E$5:$H$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F50" s="106">
         <f>COUNTIF($I$5:$N$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G50" s="106">
         <f>COUNTIF($O$5:$V$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H50" s="106">
         <f>COUNTIF($C$5:$D$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I50" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -11708,23 +11708,23 @@
       </c>
       <c r="E51" s="106">
         <f>COUNTIF($E$5:$H$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F51" s="106">
         <f>COUNTIF($I$5:$N$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G51" s="106">
         <f>COUNTIF($O$5:$V$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H51" s="106">
         <f>COUNTIF($C$5:$D$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I51" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -11743,23 +11743,23 @@
       </c>
       <c r="E53" s="107">
         <f>COUNTIF($E$5:$H$21,"*Johnson*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F53" s="107">
         <f>COUNTIF($I$5:$N$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G53" s="107">
         <f>COUNTIF($O$5:$V$21,"*Johnson*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H53" s="107">
         <f>COUNTIF($C$5:$D$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I53" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -11770,23 +11770,23 @@
       </c>
       <c r="E54" s="107">
         <f>COUNTIF($E$5:$H$21,"*Lux*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F54" s="107">
         <f>COUNTIF($I$5:$N$21,"*Lux*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G54" s="107">
         <f>COUNTIF($O$5:$V$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H54" s="107">
         <f>COUNTIF($C$5:$D$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I54" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -11797,23 +11797,23 @@
       </c>
       <c r="E55" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F55" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G55" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H55" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I55" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -11824,45 +11824,45 @@
       </c>
       <c r="E56" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mudondo*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F56" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mudondo*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G56" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H56" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I56" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="E57" s="95">
         <f>SUM(E38:E56)</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="F57" s="95">
         <f>SUM(F38:F56)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="G57" s="95">
         <f>SUM(G38:G56)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="H57" s="95">
         <f>SUM(H38:H56)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="I57" s="95">
         <f>SUM(I38:I56)</f>
-        <v/>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -12302,31 +12302,31 @@
       <c r="AG6" s="205" t="n"/>
       <c r="AH6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AI6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AJ6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AL6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AM6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AN6" s="92">
         <f>SUM(AH6:AM6)</f>
-        <v/>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="9.949999999999999" customHeight="1">
@@ -12511,35 +12511,35 @@
       <c r="AG9" s="205" t="n"/>
       <c r="AH9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AI9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AJ9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AK9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AN9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AO9" s="92">
         <f>SUM(AH9:AN9)</f>
-        <v/>
+        <v>16</v>
       </c>
     </row>
     <row r="10" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -12722,23 +12722,23 @@
       <c r="AG12" s="205" t="n"/>
       <c r="AH12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AJ12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AL12" s="84">
         <f>SUM(AH12:AK12)</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="13" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -13729,23 +13729,23 @@
       </c>
       <c r="E38" s="104">
         <f>COUNTIF($E$5:$H$21,"*Hard*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F38" s="104">
         <f>COUNTIF($I$5:$N$21,"*Hard*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G38" s="104">
         <f>COUNTIF($O$5:$V$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H38" s="104">
         <f>COUNTIF($C$5:$D$21,"*Hard*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I38" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -13756,23 +13756,23 @@
       </c>
       <c r="E39" s="104">
         <f>COUNTIF($E$5:$H$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F39" s="104">
         <f>COUNTIF($I$5:$N$21,"*Oehm*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="G39" s="104">
         <f>COUNTIF($O$5:$V$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H39" s="104">
         <f>COUNTIF($C$5:$D$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I39" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -13783,23 +13783,23 @@
       </c>
       <c r="E40" s="104">
         <f>COUNTIF($E$5:$H$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F40" s="104">
         <f>COUNTIF($I$5:$N$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G40" s="104">
         <f>COUNTIF($O$5:$V$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H40" s="104">
         <f>COUNTIF($C$5:$D$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I40" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -13810,23 +13810,23 @@
       </c>
       <c r="E41" s="104">
         <f>COUNTIF($E$5:$H$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F41" s="104">
         <f>COUNTIF($I$5:$N$21,"*Stanek*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G41" s="104">
         <f>COUNTIF($O$5:$V$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H41" s="104">
         <f>COUNTIF($C$5:$D$21,"*Stanek*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I41" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -13837,23 +13837,23 @@
       </c>
       <c r="E42" s="104">
         <f>COUNTIF($E$5:$H$21,"*Strand*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F42" s="104">
         <f>COUNTIF($I$5:$N$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G42" s="104">
         <f>COUNTIF($O$5:$V$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H42" s="104">
         <f>COUNTIF($C$5:$D$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I42" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -13864,23 +13864,23 @@
       </c>
       <c r="E43" s="104">
         <f>COUNTIF($E$5:$H$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F43" s="104">
         <f>COUNTIF($I$5:$N$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G43" s="104">
         <f>COUNTIF($O$5:$V$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="H43" s="104">
         <f>COUNTIF($C$5:$D$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I43" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -13899,23 +13899,23 @@
       </c>
       <c r="E45" s="106">
         <f>COUNTIF($E$5:$H$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F45" s="106">
         <f>COUNTIF($I$5:$N$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G45" s="106">
         <f>COUNTIF($O$5:$V$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H45" s="106">
         <f>COUNTIF($C$5:$D$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I45" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -13926,23 +13926,23 @@
       </c>
       <c r="E46" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F46" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G46" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H46" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I46" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -13953,23 +13953,23 @@
       </c>
       <c r="E47" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F47" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G47" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H47" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I47" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -13980,23 +13980,23 @@
       </c>
       <c r="E48" s="106">
         <f>COUNTIF($E$5:$H$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F48" s="106">
         <f>COUNTIF($I$5:$N$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G48" s="106">
         <f>COUNTIF($O$5:$V$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H48" s="106">
         <f>COUNTIF($C$5:$D$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I48" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -14007,23 +14007,23 @@
       </c>
       <c r="E49" s="106">
         <f>COUNTIF($E$5:$H$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F49" s="106">
         <f>COUNTIF($I$5:$N$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G49" s="106">
         <f>COUNTIF($O$5:$V$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H49" s="106">
         <f>COUNTIF($C$5:$D$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I49" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -14034,23 +14034,23 @@
       </c>
       <c r="E50" s="106">
         <f>COUNTIF($E$5:$H$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F50" s="106">
         <f>COUNTIF($I$5:$N$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G50" s="106">
         <f>COUNTIF($O$5:$V$21,"*Patel*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="H50" s="106">
         <f>COUNTIF($C$5:$D$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I50" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -14061,23 +14061,23 @@
       </c>
       <c r="E51" s="106">
         <f>COUNTIF($E$5:$H$21,"*Sublette*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F51" s="106">
         <f>COUNTIF($I$5:$N$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G51" s="106">
         <f>COUNTIF($O$5:$V$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H51" s="106">
         <f>COUNTIF($C$5:$D$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I51" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -14096,23 +14096,23 @@
       </c>
       <c r="E53" s="107">
         <f>COUNTIF($E$5:$H$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F53" s="107">
         <f>COUNTIF($I$5:$N$21,"*Johnson*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G53" s="107">
         <f>COUNTIF($O$5:$V$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H53" s="107">
         <f>COUNTIF($C$5:$D$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I53" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -14123,23 +14123,23 @@
       </c>
       <c r="E54" s="107">
         <f>COUNTIF($E$5:$H$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F54" s="107">
         <f>COUNTIF($I$5:$N$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G54" s="107">
         <f>COUNTIF($O$5:$V$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H54" s="107">
         <f>COUNTIF($C$5:$D$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I54" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -14150,23 +14150,23 @@
       </c>
       <c r="E55" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F55" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G55" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H55" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I55" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -14177,45 +14177,45 @@
       </c>
       <c r="E56" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F56" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mudondo*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G56" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H56" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I56" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="E57" s="95">
         <f>SUM(E38:E56)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="F57" s="95">
         <f>SUM(F38:F56)</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="G57" s="95">
         <f>SUM(G38:G56)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="H57" s="95">
         <f>SUM(H38:H56)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="I57" s="95">
         <f>SUM(I38:I56)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -14906,31 +14906,31 @@
       <c r="A3" s="205" t="n"/>
       <c r="B3" s="95">
         <f>SUM(July:June!AH6)</f>
-        <v/>
+        <v>56</v>
       </c>
       <c r="C3" s="95">
         <f>SUM(July:June!AI6)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="D3" s="95">
         <f>SUM(July:June!AJ6)</f>
-        <v/>
+        <v>56</v>
       </c>
       <c r="E3" s="95">
         <f>SUM(July:June!AK6)</f>
-        <v/>
+        <v>57</v>
       </c>
       <c r="F3" s="95">
         <f>SUM(July:June!AL6)</f>
-        <v/>
+        <v>58</v>
       </c>
       <c r="G3" s="95">
         <f>SUM(July:June!AM6)</f>
-        <v/>
+        <v>57</v>
       </c>
       <c r="H3" s="95">
         <f>SUM(B3:G3)</f>
-        <v/>
+        <v>339</v>
       </c>
       <c r="K3" s="109" t="inlineStr">
         <is>
@@ -15010,35 +15010,35 @@
       <c r="A6" s="205" t="n"/>
       <c r="B6" s="97">
         <f>SUM(July:June!AH9)</f>
-        <v/>
+        <v>34</v>
       </c>
       <c r="C6" s="97">
         <f>SUM(July:June!AI9)</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="D6" s="97">
         <f>SUM(July:June!AJ9)</f>
-        <v/>
+        <v>34</v>
       </c>
       <c r="E6" s="97">
         <f>SUM(July:June!AK9)</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="F6" s="97">
         <f>SUM(July:June!AL9)</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="G6" s="97">
         <f>SUM(July:June!AM9)</f>
-        <v/>
+        <v>35</v>
       </c>
       <c r="H6" s="97">
         <f>SUM(July:June!AN9)</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="I6" s="95">
         <f>SUM(B6:H6)</f>
-        <v/>
+        <v>235</v>
       </c>
       <c r="K6" s="98" t="inlineStr">
         <is>
@@ -15100,23 +15100,23 @@
       <c r="A9" s="205" t="n"/>
       <c r="B9" s="94">
         <f>SUM(July:June!AH12)</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="C9" s="94">
         <f>SUM(July:June!AI12)</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="D9" s="94">
         <f>SUM(July:June!AJ12)</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="E9" s="94">
         <f>SUM(July:June!AK12)</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="F9" s="95">
         <f>SUM(B9:E9)</f>
-        <v/>
+        <v>132</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -15163,23 +15163,23 @@
       </c>
       <c r="B13" s="104">
         <f>SUM(July:June!E38)</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="C13" s="104">
         <f>SUM(July:June!F38)</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="D13" s="104">
         <f>SUM(July:June!G38)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="E13" s="104">
         <f>SUM(July:June!H38)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="F13" s="104">
         <f>SUM(July:June!I38)</f>
-        <v/>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -15190,23 +15190,23 @@
       </c>
       <c r="B14" s="104">
         <f>SUM(July:June!E39)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="C14" s="104">
         <f>SUM(July:June!F39)</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="D14" s="104">
         <f>SUM(July:June!G39)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="E14" s="104">
         <f>SUM(July:June!H39)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="F14" s="104">
         <f>SUM(July:June!I39)</f>
-        <v/>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -15217,23 +15217,23 @@
       </c>
       <c r="B15" s="104">
         <f>SUM(July:June!E40)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="C15" s="104">
         <f>SUM(July:June!F40)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="D15" s="104">
         <f>SUM(July:June!G40)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="E15" s="104">
         <f>SUM(July:June!H40)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="F15" s="104">
         <f>SUM(July:June!I40)</f>
-        <v/>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -15244,23 +15244,23 @@
       </c>
       <c r="B16" s="104">
         <f>SUM(July:June!E41)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="C16" s="104">
         <f>SUM(July:June!F41)</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="D16" s="104">
         <f>SUM(July:June!G41)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="E16" s="104">
         <f>SUM(July:June!H41)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="F16" s="104">
         <f>SUM(July:June!I41)</f>
-        <v/>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -15271,23 +15271,23 @@
       </c>
       <c r="B17" s="104">
         <f>SUM(July:June!E42)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="C17" s="104">
         <f>SUM(July:June!F42)</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="D17" s="104">
         <f>SUM(July:June!G42)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="E17" s="104">
         <f>SUM(July:June!H42)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="F17" s="104">
         <f>SUM(July:June!I42)</f>
-        <v/>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -15298,23 +15298,23 @@
       </c>
       <c r="B18" s="104">
         <f>SUM(July:June!E43)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="C18" s="104">
         <f>SUM(July:June!F43)</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="D18" s="104">
         <f>SUM(July:June!G43)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="E18" s="104">
         <f>SUM(July:June!H43)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="F18" s="104">
         <f>SUM(July:June!I43)</f>
-        <v/>
+        <v>8</v>
       </c>
     </row>
     <row r="19" ht="7.15" customHeight="1">
@@ -15333,23 +15333,23 @@
       </c>
       <c r="B20" s="106">
         <f>SUM(July:June!E45)</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="C20" s="106">
         <f>SUM(July:June!F45)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="D20" s="106">
         <f>SUM(July:June!G45)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E20" s="106">
         <f>SUM(July:June!H45)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="F20" s="106">
         <f>SUM(July:June!I45)</f>
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -15360,23 +15360,23 @@
       </c>
       <c r="B21" s="106">
         <f>SUM(July:June!E46)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="C21" s="106">
         <f>SUM(July:June!F46)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="D21" s="106">
         <f>SUM(July:June!G46)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E21" s="106">
         <f>SUM(July:June!H46)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="F21" s="106">
         <f>SUM(July:June!I46)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -15387,23 +15387,23 @@
       </c>
       <c r="B22" s="106">
         <f>SUM(July:June!E47)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="C22" s="106">
         <f>SUM(July:June!F47)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="D22" s="106">
         <f>SUM(July:June!G47)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E22" s="106">
         <f>SUM(July:June!H47)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="F22" s="106">
         <f>SUM(July:June!I47)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -15414,23 +15414,23 @@
       </c>
       <c r="B23" s="106">
         <f>SUM(July:June!E48)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="C23" s="106">
         <f>SUM(July:June!F48)</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="D23" s="106">
         <f>SUM(July:June!G48)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="E23" s="106">
         <f>SUM(July:June!H48)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="F23" s="106">
         <f>SUM(July:June!I48)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -15441,23 +15441,23 @@
       </c>
       <c r="B24" s="106">
         <f>SUM(July:June!E49)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="C24" s="106">
         <f>SUM(July:June!F49)</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="D24" s="106">
         <f>SUM(July:June!G49)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E24" s="106">
         <f>SUM(July:June!H49)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="F24" s="106">
         <f>SUM(July:June!I49)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -15468,23 +15468,23 @@
       </c>
       <c r="B25" s="106">
         <f>SUM(July:June!E50)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="C25" s="106">
         <f>SUM(July:June!F50)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="D25" s="106">
         <f>SUM(July:June!G50)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="E25" s="106">
         <f>SUM(July:June!H50)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="F25" s="106">
         <f>SUM(July:June!I50)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -15495,23 +15495,23 @@
       </c>
       <c r="B26" s="106">
         <f>SUM(July:June!E51)</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="C26" s="106">
         <f>SUM(July:June!F51)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="D26" s="106">
         <f>SUM(July:June!G51)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E26" s="106">
         <f>SUM(July:June!H51)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="F26" s="106">
         <f>SUM(July:June!I51)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="27" ht="7.9" customHeight="1">
@@ -15530,23 +15530,23 @@
       </c>
       <c r="B28" s="107">
         <f>SUM(July:June!E53)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="C28" s="107">
         <f>SUM(July:June!F53)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="D28" s="107">
         <f>SUM(July:June!G53)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="E28" s="107">
         <f>SUM(July:June!H53)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F28" s="107">
         <f>SUM(July:June!I53)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -15557,23 +15557,23 @@
       </c>
       <c r="B29" s="107">
         <f>SUM(July:June!E54)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="C29" s="107">
         <f>SUM(July:June!F54)</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="D29" s="107">
         <f>SUM(July:June!G54)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="E29" s="107">
         <f>SUM(July:June!H54)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F29" s="107">
         <f>SUM(July:June!I54)</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -15584,23 +15584,23 @@
       </c>
       <c r="B30" s="107">
         <f>SUM(July:June!E55)</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="C30" s="107">
         <f>SUM(July:June!F55)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="D30" s="107">
         <f>SUM(July:June!G55)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="E30" s="107">
         <f>SUM(July:June!H55)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F30" s="107">
         <f>SUM(July:June!I55)</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -15611,45 +15611,45 @@
       </c>
       <c r="B31" s="107">
         <f>SUM(July:June!E56)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="C31" s="107">
         <f>SUM(July:June!F56)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="D31" s="107">
         <f>SUM(July:June!G56)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="E31" s="107">
         <f>SUM(July:June!H56)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F31" s="107">
         <f>SUM(July:June!I56)</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="95">
         <f>SUM(B13:B31)</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="C32" s="95">
         <f>SUM(C13:C31)</f>
-        <v/>
+        <v>204</v>
       </c>
       <c r="D32" s="95">
         <f>SUM(D13:D31)</f>
-        <v/>
+        <v>101</v>
       </c>
       <c r="E32" s="95">
         <f>SUM(E13:E31)</f>
-        <v/>
+        <v>99</v>
       </c>
       <c r="F32" s="95">
         <f>SUM(F13:F31)</f>
-        <v/>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -15950,31 +15950,31 @@
       <c r="AG6" s="205" t="n"/>
       <c r="AH6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AI6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AJ6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="AK6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AL6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AM6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AN6" s="92">
         <f>SUM(AH6:AM6)</f>
-        <v/>
+        <v>31</v>
       </c>
     </row>
     <row r="7" ht="9.949999999999999" customHeight="1">
@@ -16158,35 +16158,35 @@
       <c r="AG9" s="205" t="n"/>
       <c r="AH9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AJ9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AK9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AL9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AM9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AN9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AO9" s="92">
         <f>SUM(AH9:AN9)</f>
-        <v/>
+        <v>23</v>
       </c>
     </row>
     <row r="10" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -16369,23 +16369,23 @@
       <c r="AG12" s="205" t="n"/>
       <c r="AH12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AI12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AJ12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AL12" s="84">
         <f>SUM(AH12:AK12)</f>
-        <v/>
+        <v>11</v>
       </c>
     </row>
     <row r="13" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -17452,23 +17452,23 @@
       </c>
       <c r="E38" s="104">
         <f>COUNTIF($E$5:$H$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F38" s="104">
         <f>COUNTIF($I$5:$N$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G38" s="104">
         <f>COUNTIF($O$5:$V$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H38" s="104">
         <f>COUNTIF($C$5:$D$21,"*Hard*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="I38" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -17479,23 +17479,23 @@
       </c>
       <c r="E39" s="104">
         <f>COUNTIF($E$5:$H$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F39" s="104">
         <f>COUNTIF($I$5:$N$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G39" s="104">
         <f>COUNTIF($O$5:$V$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H39" s="104">
         <f>COUNTIF($C$5:$D$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I39" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -17506,23 +17506,23 @@
       </c>
       <c r="E40" s="104">
         <f>COUNTIF($E$5:$H$21,"*Schutt*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F40" s="104">
         <f>COUNTIF($I$5:$N$21,"*Schutt*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="G40" s="104">
         <f>COUNTIF($O$5:$V$21,"*Schutt*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="H40" s="104">
         <f>COUNTIF($C$5:$D$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I40" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -17533,23 +17533,23 @@
       </c>
       <c r="E41" s="104">
         <f>COUNTIF($E$5:$H$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F41" s="104">
         <f>COUNTIF($I$5:$N$21,"*Stanek*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G41" s="104">
         <f>COUNTIF($O$5:$V$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H41" s="104">
         <f>COUNTIF($C$5:$D$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I41" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -17560,23 +17560,23 @@
       </c>
       <c r="E42" s="104">
         <f>COUNTIF($E$5:$H$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F42" s="104">
         <f>COUNTIF($I$5:$N$21,"*Strand*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G42" s="104">
         <f>COUNTIF($O$5:$V$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H42" s="104">
         <f>COUNTIF($C$5:$D$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I42" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -17587,23 +17587,23 @@
       </c>
       <c r="E43" s="104">
         <f>COUNTIF($E$5:$H$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F43" s="104">
         <f>COUNTIF($I$5:$N$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="G43" s="104">
         <f>COUNTIF($O$5:$V$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H43" s="104">
         <f>COUNTIF($C$5:$D$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I43" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -17622,23 +17622,23 @@
       </c>
       <c r="E45" s="106">
         <f>COUNTIF($E$5:$H$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F45" s="106">
         <f>COUNTIF($I$5:$N$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G45" s="106">
         <f>COUNTIF($O$5:$V$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H45" s="106">
         <f>COUNTIF($C$5:$D$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I45" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -17649,23 +17649,23 @@
       </c>
       <c r="E46" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F46" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G46" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H46" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I46" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -17676,23 +17676,23 @@
       </c>
       <c r="E47" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F47" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G47" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bower*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H47" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I47" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -17703,23 +17703,23 @@
       </c>
       <c r="E48" s="106">
         <f>COUNTIF($E$5:$H$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F48" s="106">
         <f>COUNTIF($I$5:$N$21,"*Gaspar*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="G48" s="106">
         <f>COUNTIF($O$5:$V$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H48" s="106">
         <f>COUNTIF($C$5:$D$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I48" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -17730,23 +17730,23 @@
       </c>
       <c r="E49" s="106">
         <f>COUNTIF($E$5:$H$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F49" s="106">
         <f>COUNTIF($I$5:$N$21,"*Kendrick*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G49" s="106">
         <f>COUNTIF($O$5:$V$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H49" s="106">
         <f>COUNTIF($C$5:$D$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I49" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -17757,23 +17757,23 @@
       </c>
       <c r="E50" s="106">
         <f>COUNTIF($E$5:$H$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F50" s="106">
         <f>COUNTIF($I$5:$N$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G50" s="106">
         <f>COUNTIF($O$5:$V$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H50" s="106">
         <f>COUNTIF($C$5:$D$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I50" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -17784,23 +17784,23 @@
       </c>
       <c r="E51" s="106">
         <f>COUNTIF($E$5:$H$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F51" s="106">
         <f>COUNTIF($I$5:$N$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G51" s="106">
         <f>COUNTIF($O$5:$V$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H51" s="106">
         <f>COUNTIF($C$5:$D$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I51" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -17819,23 +17819,23 @@
       </c>
       <c r="E53" s="107">
         <f>COUNTIF($E$5:$H$21,"*Johnson*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F53" s="107">
         <f>COUNTIF($I$5:$N$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G53" s="107">
         <f>COUNTIF($O$5:$V$21,"*Johnson*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H53" s="107">
         <f>COUNTIF($C$5:$D$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I53" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -17846,23 +17846,23 @@
       </c>
       <c r="E54" s="107">
         <f>COUNTIF($E$5:$H$21,"*Lux*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F54" s="107">
         <f>COUNTIF($I$5:$N$21,"*Lux*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G54" s="107">
         <f>COUNTIF($O$5:$V$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H54" s="107">
         <f>COUNTIF($C$5:$D$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I54" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -17873,23 +17873,23 @@
       </c>
       <c r="E55" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mautino*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F55" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mautino*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G55" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H55" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I55" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -17900,45 +17900,45 @@
       </c>
       <c r="E56" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F56" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G56" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H56" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I56" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="E57" s="95">
         <f>SUM(E38:E56)</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="F57" s="95">
         <f>SUM(F38:F56)</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="G57" s="95">
         <f>SUM(G38:G56)</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="H57" s="95">
         <f>SUM(H38:H56)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="I57" s="95">
         <f>SUM(I38:I56)</f>
-        <v/>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -18355,31 +18355,31 @@
       <c r="AG6" s="205" t="n"/>
       <c r="AH6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AI6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AJ6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AL6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AM6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AN6" s="94">
         <f>SUM(AH6:AM6)</f>
-        <v/>
+        <v>30</v>
       </c>
     </row>
     <row r="7" ht="9.949999999999999" customHeight="1">
@@ -18563,35 +18563,35 @@
       <c r="AG9" s="205" t="n"/>
       <c r="AH9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AI9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AJ9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AL9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AM9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AN9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AO9" s="92">
         <f>SUM(AH9:AN9)</f>
-        <v/>
+        <v>25</v>
       </c>
     </row>
     <row r="10" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -18774,23 +18774,23 @@
       <c r="AG12" s="205" t="n"/>
       <c r="AH12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AJ12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AK12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AL12" s="84">
         <f>SUM(AH12:AK12)</f>
-        <v/>
+        <v>11</v>
       </c>
     </row>
     <row r="13" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -19869,23 +19869,23 @@
       </c>
       <c r="E38" s="104">
         <f>COUNTIF($E$5:$H$21,"*Hard*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F38" s="104">
         <f>COUNTIF($I$5:$N$21,"*Hard*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="G38" s="104">
         <f>COUNTIF($O$5:$V$21,"*Hard*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H38" s="104">
         <f>COUNTIF($C$5:$D$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I38" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -19896,23 +19896,23 @@
       </c>
       <c r="E39" s="104">
         <f>COUNTIF($E$5:$H$21,"*Oehm*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F39" s="104">
         <f>COUNTIF($I$5:$N$21,"*Oehm*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="G39" s="104">
         <f>COUNTIF($O$5:$V$21,"*Oehm*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H39" s="104">
         <f>COUNTIF($C$5:$D$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I39" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -19923,23 +19923,23 @@
       </c>
       <c r="E40" s="104">
         <f>COUNTIF($E$5:$H$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F40" s="104">
         <f>COUNTIF($I$5:$N$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G40" s="104">
         <f>COUNTIF($O$5:$V$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H40" s="104">
         <f>COUNTIF($C$5:$D$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I40" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -19950,23 +19950,23 @@
       </c>
       <c r="E41" s="104">
         <f>COUNTIF($E$5:$H$21,"*Stanek*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F41" s="104">
         <f>COUNTIF($I$5:$N$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G41" s="104">
         <f>COUNTIF($O$5:$V$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H41" s="104">
         <f>COUNTIF($C$5:$D$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I41" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -19977,23 +19977,23 @@
       </c>
       <c r="E42" s="104">
         <f>COUNTIF($E$5:$H$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F42" s="104">
         <f>COUNTIF($I$5:$N$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G42" s="104">
         <f>COUNTIF($O$5:$V$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H42" s="104">
         <f>COUNTIF($C$5:$D$21,"*Strand*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="I42" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -20004,23 +20004,23 @@
       </c>
       <c r="E43" s="104">
         <f>COUNTIF($E$5:$H$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F43" s="104">
         <f>COUNTIF($I$5:$N$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G43" s="104">
         <f>COUNTIF($O$5:$V$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H43" s="104">
         <f>COUNTIF($C$5:$D$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I43" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -20039,23 +20039,23 @@
       </c>
       <c r="E45" s="106">
         <f>COUNTIF($E$5:$H$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F45" s="106">
         <f>COUNTIF($I$5:$N$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G45" s="106">
         <f>COUNTIF($O$5:$V$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H45" s="106">
         <f>COUNTIF($C$5:$D$21,"*Beutel*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I45" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -20066,23 +20066,23 @@
       </c>
       <c r="E46" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F46" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G46" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H46" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I46" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -20093,23 +20093,23 @@
       </c>
       <c r="E47" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F47" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G47" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H47" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I47" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -20120,23 +20120,23 @@
       </c>
       <c r="E48" s="106">
         <f>COUNTIF($E$5:$H$21,"*Gaspar*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F48" s="106">
         <f>COUNTIF($I$5:$N$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G48" s="106">
         <f>COUNTIF($O$5:$V$21,"*Gaspar*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="H48" s="106">
         <f>COUNTIF($C$5:$D$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I48" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -20147,23 +20147,23 @@
       </c>
       <c r="E49" s="106">
         <f>COUNTIF($E$5:$H$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F49" s="106">
         <f>COUNTIF($I$5:$N$21,"*Kendrick*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G49" s="106">
         <f>COUNTIF($O$5:$V$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H49" s="106">
         <f>COUNTIF($C$5:$D$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I49" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -20174,23 +20174,23 @@
       </c>
       <c r="E50" s="106">
         <f>COUNTIF($E$5:$H$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F50" s="106">
         <f>COUNTIF($I$5:$N$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G50" s="106">
         <f>COUNTIF($O$5:$V$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H50" s="106">
         <f>COUNTIF($C$5:$D$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I50" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -20201,23 +20201,23 @@
       </c>
       <c r="E51" s="106">
         <f>COUNTIF($E$5:$H$21,"*Sublette*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F51" s="106">
         <f>COUNTIF($I$5:$N$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G51" s="106">
         <f>COUNTIF($O$5:$V$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H51" s="106">
         <f>COUNTIF($C$5:$D$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I51" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -20236,23 +20236,23 @@
       </c>
       <c r="E53" s="107">
         <f>COUNTIF($E$5:$H$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F53" s="107">
         <f>COUNTIF($I$5:$N$21,"*Johnson*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G53" s="107">
         <f>COUNTIF($O$5:$V$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H53" s="107">
         <f>COUNTIF($C$5:$D$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I53" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -20263,23 +20263,23 @@
       </c>
       <c r="E54" s="107">
         <f>COUNTIF($E$5:$H$21,"*Lux*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F54" s="107">
         <f>COUNTIF($I$5:$N$21,"*Lux*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G54" s="107">
         <f>COUNTIF($O$5:$V$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H54" s="107">
         <f>COUNTIF($C$5:$D$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I54" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -20290,23 +20290,23 @@
       </c>
       <c r="E55" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mautino*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F55" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G55" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H55" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I55" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -20317,45 +20317,45 @@
       </c>
       <c r="E56" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mudondo*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F56" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mudondo*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="G56" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H56" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I56" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="E57" s="95">
         <f>SUM(E38:E56)</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="F57" s="95">
         <f>SUM(F38:F56)</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="G57" s="95">
         <f>SUM(G38:G56)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="H57" s="95">
         <f>SUM(H38:H56)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="I57" s="95">
         <f>SUM(I38:I56)</f>
-        <v/>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -20792,31 +20792,31 @@
       <c r="AG6" s="205" t="n"/>
       <c r="AH6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AJ6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AK6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AL6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AM6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AN6" s="92">
         <f>SUM(AH6:AM6)</f>
-        <v/>
+        <v>30</v>
       </c>
     </row>
     <row r="7" ht="9.949999999999999" customHeight="1">
@@ -21000,35 +21000,35 @@
       <c r="AG9" s="205" t="n"/>
       <c r="AH9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AJ9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AK9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AL9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AM9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AN9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AO9" s="92">
         <f>SUM(AH9:AN9)</f>
-        <v/>
+        <v>20</v>
       </c>
     </row>
     <row r="10" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -21211,23 +21211,23 @@
       <c r="AG12" s="205" t="n"/>
       <c r="AH12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AI12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AJ12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AK12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AL12" s="84">
         <f>SUM(AH12:AK12)</f>
-        <v/>
+        <v>15</v>
       </c>
     </row>
     <row r="13" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -22287,23 +22287,23 @@
       </c>
       <c r="E38" s="104">
         <f>COUNTIF($E$5:$H$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F38" s="104">
         <f>COUNTIF($I$5:$N$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G38" s="104">
         <f>COUNTIF($O$5:$V$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H38" s="104">
         <f>COUNTIF($C$5:$D$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I38" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -22314,23 +22314,23 @@
       </c>
       <c r="E39" s="104">
         <f>COUNTIF($E$5:$H$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F39" s="104">
         <f>COUNTIF($I$5:$N$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G39" s="104">
         <f>COUNTIF($O$5:$V$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H39" s="104">
         <f>COUNTIF($C$5:$D$21,"*Oehm*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I39" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -22341,23 +22341,23 @@
       </c>
       <c r="E40" s="104">
         <f>COUNTIF($E$5:$H$21,"*Schutt*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F40" s="104">
         <f>COUNTIF($I$5:$N$21,"*Schutt*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G40" s="104">
         <f>COUNTIF($O$5:$V$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H40" s="104">
         <f>COUNTIF($C$5:$D$21,"*Schutt*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I40" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -22368,23 +22368,23 @@
       </c>
       <c r="E41" s="104">
         <f>COUNTIF($E$5:$H$21,"*Stanek*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F41" s="104">
         <f>COUNTIF($I$5:$N$21,"*Stanek*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="G41" s="104">
         <f>COUNTIF($O$5:$V$21,"*Stanek*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H41" s="104">
         <f>COUNTIF($C$5:$D$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I41" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -22395,23 +22395,23 @@
       </c>
       <c r="E42" s="104">
         <f>COUNTIF($E$5:$H$21,"*Strand*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F42" s="104">
         <f>COUNTIF($I$5:$N$21,"*Strand*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="G42" s="104">
         <f>COUNTIF($O$5:$V$21,"*Strand*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H42" s="104">
         <f>COUNTIF($C$5:$D$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I42" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -22422,23 +22422,23 @@
       </c>
       <c r="E43" s="104">
         <f>COUNTIF($E$5:$H$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F43" s="104">
         <f>COUNTIF($I$5:$N$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G43" s="104">
         <f>COUNTIF($O$5:$V$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H43" s="104">
         <f>COUNTIF($C$5:$D$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I43" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -22457,23 +22457,23 @@
       </c>
       <c r="E45" s="106">
         <f>COUNTIF($E$5:$H$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F45" s="106">
         <f>COUNTIF($I$5:$N$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G45" s="106">
         <f>COUNTIF($O$5:$V$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H45" s="106">
         <f>COUNTIF($C$5:$D$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I45" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -22484,23 +22484,23 @@
       </c>
       <c r="E46" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F46" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G46" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H46" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I46" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -22511,23 +22511,23 @@
       </c>
       <c r="E47" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F47" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G47" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H47" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I47" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -22538,23 +22538,23 @@
       </c>
       <c r="E48" s="106">
         <f>COUNTIF($E$5:$H$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F48" s="106">
         <f>COUNTIF($I$5:$N$21,"*Gaspar*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G48" s="106">
         <f>COUNTIF($O$5:$V$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H48" s="106">
         <f>COUNTIF($C$5:$D$21,"*Gaspar*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I48" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -22565,23 +22565,23 @@
       </c>
       <c r="E49" s="106">
         <f>COUNTIF($E$5:$H$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F49" s="106">
         <f>COUNTIF($I$5:$N$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G49" s="106">
         <f>COUNTIF($O$5:$V$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H49" s="106">
         <f>COUNTIF($C$5:$D$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I49" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -22592,23 +22592,23 @@
       </c>
       <c r="E50" s="106">
         <f>COUNTIF($E$5:$H$21,"*Patel*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F50" s="106">
         <f>COUNTIF($I$5:$N$21,"*Patel*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G50" s="106">
         <f>COUNTIF($O$5:$V$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H50" s="106">
         <f>COUNTIF($C$5:$D$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I50" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -22619,23 +22619,23 @@
       </c>
       <c r="E51" s="106">
         <f>COUNTIF($E$5:$H$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F51" s="106">
         <f>COUNTIF($I$5:$N$21,"*Sublette*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G51" s="106">
         <f>COUNTIF($O$5:$V$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H51" s="106">
         <f>COUNTIF($C$5:$D$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I51" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -22654,23 +22654,23 @@
       </c>
       <c r="E53" s="107">
         <f>COUNTIF($E$5:$H$21,"*Johnson*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F53" s="107">
         <f>COUNTIF($I$5:$N$21,"*Johnson*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G53" s="107">
         <f>COUNTIF($O$5:$V$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H53" s="107">
         <f>COUNTIF($C$5:$D$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I53" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -22681,23 +22681,23 @@
       </c>
       <c r="E54" s="107">
         <f>COUNTIF($E$5:$H$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F54" s="107">
         <f>COUNTIF($I$5:$N$21,"*Lux*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="G54" s="107">
         <f>COUNTIF($O$5:$V$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H54" s="107">
         <f>COUNTIF($C$5:$D$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I54" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -22708,23 +22708,23 @@
       </c>
       <c r="E55" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mautino*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F55" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G55" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H55" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I55" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -22735,45 +22735,45 @@
       </c>
       <c r="E56" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mudondo*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F56" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G56" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mudondo*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="H56" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I56" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="E57" s="95">
         <f>SUM(E38:E56)</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="F57" s="95">
         <f>SUM(F38:F56)</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="G57" s="95">
         <f>SUM(G38:G56)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="H57" s="95">
         <f>SUM(H38:H56)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="I57" s="95">
         <f>SUM(I38:I56)</f>
-        <v/>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -23201,31 +23201,31 @@
       <c r="AG6" s="205" t="n"/>
       <c r="AH6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AJ6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AK6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AL6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AN6" s="92">
         <f>SUM(AH6:AM6)</f>
-        <v/>
+        <v>31</v>
       </c>
     </row>
     <row r="7" ht="9.949999999999999" customHeight="1">
@@ -23410,35 +23410,35 @@
       <c r="AG9" s="205" t="n"/>
       <c r="AH9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AI9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AJ9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AK9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AL9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AM9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AN9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AO9" s="92">
         <f>SUM(AH9:AN9)</f>
-        <v/>
+        <v>17</v>
       </c>
     </row>
     <row r="10" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -23621,23 +23621,23 @@
       <c r="AG12" s="205" t="n"/>
       <c r="AH12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AI12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AJ12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AL12" s="84">
         <f>SUM(AH12:AK12)</f>
-        <v/>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -24705,23 +24705,23 @@
       </c>
       <c r="E38" s="104">
         <f>COUNTIF($E$5:$H$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F38" s="104">
         <f>COUNTIF($I$5:$N$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G38" s="104">
         <f>COUNTIF($O$5:$V$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H38" s="104">
         <f>COUNTIF($C$5:$D$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I38" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -24732,23 +24732,23 @@
       </c>
       <c r="E39" s="104">
         <f>COUNTIF($E$5:$H$21,"*Oehm*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F39" s="104">
         <f>COUNTIF($I$5:$N$21,"*Oehm*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G39" s="104">
         <f>COUNTIF($O$5:$V$21,"*Oehm*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H39" s="104">
         <f>COUNTIF($C$5:$D$21,"*Oehm*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="I39" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -24759,23 +24759,23 @@
       </c>
       <c r="E40" s="104">
         <f>COUNTIF($E$5:$H$21,"*Schutt*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F40" s="104">
         <f>COUNTIF($I$5:$N$21,"*Schutt*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="G40" s="104">
         <f>COUNTIF($O$5:$V$21,"*Schutt*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H40" s="104">
         <f>COUNTIF($C$5:$D$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I40" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -24786,23 +24786,23 @@
       </c>
       <c r="E41" s="104">
         <f>COUNTIF($E$5:$H$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F41" s="104">
         <f>COUNTIF($I$5:$N$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G41" s="104">
         <f>COUNTIF($O$5:$V$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H41" s="104">
         <f>COUNTIF($C$5:$D$21,"*Stanek*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I41" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -24813,23 +24813,23 @@
       </c>
       <c r="E42" s="104">
         <f>COUNTIF($E$5:$H$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F42" s="104">
         <f>COUNTIF($I$5:$N$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G42" s="104">
         <f>COUNTIF($O$5:$V$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H42" s="104">
         <f>COUNTIF($C$5:$D$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I42" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -24840,23 +24840,23 @@
       </c>
       <c r="E43" s="104">
         <f>COUNTIF($E$5:$H$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F43" s="104">
         <f>COUNTIF($I$5:$N$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="G43" s="104">
         <f>COUNTIF($O$5:$V$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H43" s="104">
         <f>COUNTIF($C$5:$D$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I43" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -24875,23 +24875,23 @@
       </c>
       <c r="E45" s="106">
         <f>COUNTIF($E$5:$H$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F45" s="106">
         <f>COUNTIF($I$5:$N$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G45" s="106">
         <f>COUNTIF($O$5:$V$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H45" s="106">
         <f>COUNTIF($C$5:$D$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I45" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -24902,23 +24902,23 @@
       </c>
       <c r="E46" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F46" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G46" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H46" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I46" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -24929,23 +24929,23 @@
       </c>
       <c r="E47" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F47" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bower*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G47" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H47" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I47" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -24956,23 +24956,23 @@
       </c>
       <c r="E48" s="106">
         <f>COUNTIF($E$5:$H$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F48" s="106">
         <f>COUNTIF($I$5:$N$21,"*Gaspar*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G48" s="106">
         <f>COUNTIF($O$5:$V$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H48" s="106">
         <f>COUNTIF($C$5:$D$21,"*Gaspar*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I48" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -24983,23 +24983,23 @@
       </c>
       <c r="E49" s="106">
         <f>COUNTIF($E$5:$H$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F49" s="106">
         <f>COUNTIF($I$5:$N$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G49" s="106">
         <f>COUNTIF($O$5:$V$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H49" s="106">
         <f>COUNTIF($C$5:$D$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I49" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -25010,23 +25010,23 @@
       </c>
       <c r="E50" s="106">
         <f>COUNTIF($E$5:$H$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F50" s="106">
         <f>COUNTIF($I$5:$N$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G50" s="106">
         <f>COUNTIF($O$5:$V$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H50" s="106">
         <f>COUNTIF($C$5:$D$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I50" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -25037,23 +25037,23 @@
       </c>
       <c r="E51" s="106">
         <f>COUNTIF($E$5:$H$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F51" s="106">
         <f>COUNTIF($I$5:$N$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G51" s="106">
         <f>COUNTIF($O$5:$V$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H51" s="106">
         <f>COUNTIF($C$5:$D$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I51" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -25072,23 +25072,23 @@
       </c>
       <c r="E53" s="107">
         <f>COUNTIF($E$5:$H$21,"*Johnson*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F53" s="107">
         <f>COUNTIF($I$5:$N$21,"*Johnson*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G53" s="107">
         <f>COUNTIF($O$5:$V$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H53" s="107">
         <f>COUNTIF($C$5:$D$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I53" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -25099,23 +25099,23 @@
       </c>
       <c r="E54" s="107">
         <f>COUNTIF($E$5:$H$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F54" s="107">
         <f>COUNTIF($I$5:$N$21,"*Lux*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G54" s="107">
         <f>COUNTIF($O$5:$V$21,"*Lux*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H54" s="107">
         <f>COUNTIF($C$5:$D$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I54" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -25126,23 +25126,23 @@
       </c>
       <c r="E55" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mautino*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F55" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G55" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mautino*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="H55" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I55" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -25153,45 +25153,45 @@
       </c>
       <c r="E56" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mudondo*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F56" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mudondo*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G56" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H56" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I56" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="E57" s="95">
         <f>SUM(E38:E56)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="F57" s="95">
         <f>SUM(F38:F56)</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="G57" s="95">
         <f>SUM(G38:G56)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="H57" s="95">
         <f>SUM(H38:H56)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="I57" s="95">
         <f>SUM(I38:I56)</f>
-        <v/>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -25639,31 +25639,31 @@
       <c r="AG6" s="205" t="n"/>
       <c r="AH6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AI6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AJ6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AK6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="AL6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AN6" s="92">
         <f>SUM(AH6:AM6)</f>
-        <v/>
+        <v>30</v>
       </c>
     </row>
     <row r="7" ht="9.949999999999999" customHeight="1">
@@ -25847,35 +25847,35 @@
       <c r="AG9" s="205" t="n"/>
       <c r="AH9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AI9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AJ9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AL9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AM9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AN9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO9" s="92">
         <f>SUM(AH9:AN9)</f>
-        <v/>
+        <v>20</v>
       </c>
     </row>
     <row r="10" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -26058,23 +26058,23 @@
       <c r="AG12" s="205" t="n"/>
       <c r="AH12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AI12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AJ12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AK12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AL12" s="84">
         <f>SUM(AH12:AK12)</f>
-        <v/>
+        <v>10</v>
       </c>
     </row>
     <row r="13" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -27111,23 +27111,23 @@
       </c>
       <c r="E38" s="104">
         <f>COUNTIF($E$5:$H$21,"*Hard*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F38" s="104">
         <f>COUNTIF($I$5:$N$21,"*Hard*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="G38" s="104">
         <f>COUNTIF($O$5:$V$21,"*Hard*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H38" s="104">
         <f>COUNTIF($C$5:$D$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I38" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -27138,23 +27138,23 @@
       </c>
       <c r="E39" s="104">
         <f>COUNTIF($E$5:$H$21,"*Oehm*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F39" s="104">
         <f>COUNTIF($I$5:$N$21,"*Oehm*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G39" s="104">
         <f>COUNTIF($O$5:$V$21,"*Oehm*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H39" s="104">
         <f>COUNTIF($C$5:$D$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I39" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -27165,23 +27165,23 @@
       </c>
       <c r="E40" s="104">
         <f>COUNTIF($E$5:$H$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F40" s="104">
         <f>COUNTIF($I$5:$N$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G40" s="104">
         <f>COUNTIF($O$5:$V$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H40" s="104">
         <f>COUNTIF($C$5:$D$21,"*Schutt*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I40" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -27192,23 +27192,23 @@
       </c>
       <c r="E41" s="104">
         <f>COUNTIF($E$5:$H$21,"*Stanek*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F41" s="104">
         <f>COUNTIF($I$5:$N$21,"*Stanek*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G41" s="104">
         <f>COUNTIF($O$5:$V$21,"*Stanek*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H41" s="104">
         <f>COUNTIF($C$5:$D$21,"*Stanek*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="I41" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -27219,23 +27219,23 @@
       </c>
       <c r="E42" s="104">
         <f>COUNTIF($E$5:$H$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F42" s="104">
         <f>COUNTIF($I$5:$N$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G42" s="104">
         <f>COUNTIF($O$5:$V$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H42" s="104">
         <f>COUNTIF($C$5:$D$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I42" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -27246,23 +27246,23 @@
       </c>
       <c r="E43" s="104">
         <f>COUNTIF($E$5:$H$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F43" s="104">
         <f>COUNTIF($I$5:$N$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G43" s="104">
         <f>COUNTIF($O$5:$V$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H43" s="104">
         <f>COUNTIF($C$5:$D$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I43" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -27281,23 +27281,23 @@
       </c>
       <c r="E45" s="106">
         <f>COUNTIF($E$5:$H$21,"*Beutel*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F45" s="106">
         <f>COUNTIF($I$5:$N$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G45" s="106">
         <f>COUNTIF($O$5:$V$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H45" s="106">
         <f>COUNTIF($C$5:$D$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I45" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -27308,23 +27308,23 @@
       </c>
       <c r="E46" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F46" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G46" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H46" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I46" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -27335,23 +27335,23 @@
       </c>
       <c r="E47" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F47" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G47" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H47" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I47" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -27362,23 +27362,23 @@
       </c>
       <c r="E48" s="106">
         <f>COUNTIF($E$5:$H$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F48" s="106">
         <f>COUNTIF($I$5:$N$21,"*Gaspar*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G48" s="106">
         <f>COUNTIF($O$5:$V$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H48" s="106">
         <f>COUNTIF($C$5:$D$21,"*Gaspar*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I48" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -27389,23 +27389,23 @@
       </c>
       <c r="E49" s="106">
         <f>COUNTIF($E$5:$H$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F49" s="106">
         <f>COUNTIF($I$5:$N$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G49" s="106">
         <f>COUNTIF($O$5:$V$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H49" s="106">
         <f>COUNTIF($C$5:$D$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I49" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -27416,23 +27416,23 @@
       </c>
       <c r="E50" s="106">
         <f>COUNTIF($E$5:$H$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F50" s="106">
         <f>COUNTIF($I$5:$N$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G50" s="106">
         <f>COUNTIF($O$5:$V$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H50" s="106">
         <f>COUNTIF($C$5:$D$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I50" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -27443,23 +27443,23 @@
       </c>
       <c r="E51" s="106">
         <f>COUNTIF($E$5:$H$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F51" s="106">
         <f>COUNTIF($I$5:$N$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G51" s="106">
         <f>COUNTIF($O$5:$V$21,"*Sublette*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H51" s="106">
         <f>COUNTIF($C$5:$D$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I51" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -27478,23 +27478,23 @@
       </c>
       <c r="E53" s="107">
         <f>COUNTIF($E$5:$H$21,"*Johnson*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F53" s="107">
         <f>COUNTIF($I$5:$N$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G53" s="107">
         <f>COUNTIF($O$5:$V$21,"*Johnson*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H53" s="107">
         <f>COUNTIF($C$5:$D$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I53" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -27505,23 +27505,23 @@
       </c>
       <c r="E54" s="107">
         <f>COUNTIF($E$5:$H$21,"*Lux*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F54" s="107">
         <f>COUNTIF($I$5:$N$21,"*Lux*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G54" s="107">
         <f>COUNTIF($O$5:$V$21,"*Lux*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H54" s="107">
         <f>COUNTIF($C$5:$D$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I54" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -27532,23 +27532,23 @@
       </c>
       <c r="E55" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F55" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G55" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H55" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I55" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -27559,45 +27559,45 @@
       </c>
       <c r="E56" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F56" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mudondo*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G56" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H56" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I56" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="E57" s="95">
         <f>SUM(E38:E56)</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="F57" s="95">
         <f>SUM(F38:F56)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="G57" s="95">
         <f>SUM(G38:G56)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="H57" s="95">
         <f>SUM(H38:H56)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="I57" s="95">
         <f>SUM(I38:I56)</f>
-        <v/>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -28037,31 +28037,31 @@
       <c r="AG6" s="205" t="n"/>
       <c r="AH6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AJ6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AL6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AM6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AN6" s="92">
         <f>SUM(AH6:AM6)</f>
-        <v/>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="9.949999999999999" customHeight="1">
@@ -28245,35 +28245,35 @@
       <c r="AG9" s="205" t="n"/>
       <c r="AH9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AI9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AJ9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AK9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AL9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AN9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AO9" s="92">
         <f>SUM(AH9:AN9)</f>
-        <v/>
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -28456,23 +28456,23 @@
       <c r="AG12" s="205" t="n"/>
       <c r="AH12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AJ12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AK12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AL12" s="84">
         <f>SUM(AH12:AK12)</f>
-        <v/>
+        <v>12</v>
       </c>
     </row>
     <row r="13" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -29518,23 +29518,23 @@
       </c>
       <c r="E38" s="104">
         <f>COUNTIF($E$5:$H$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F38" s="104">
         <f>COUNTIF($I$5:$N$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G38" s="104">
         <f>COUNTIF($O$5:$V$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H38" s="104">
         <f>COUNTIF($C$5:$D$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I38" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -29545,23 +29545,23 @@
       </c>
       <c r="E39" s="104">
         <f>COUNTIF($E$5:$H$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F39" s="104">
         <f>COUNTIF($I$5:$N$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G39" s="104">
         <f>COUNTIF($O$5:$V$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H39" s="104">
         <f>COUNTIF($C$5:$D$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I39" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -29572,23 +29572,23 @@
       </c>
       <c r="E40" s="104">
         <f>COUNTIF($E$5:$H$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F40" s="104">
         <f>COUNTIF($I$5:$N$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G40" s="104">
         <f>COUNTIF($O$5:$V$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H40" s="104">
         <f>COUNTIF($C$5:$D$21,"*Schutt*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I40" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -29599,23 +29599,23 @@
       </c>
       <c r="E41" s="104">
         <f>COUNTIF($E$5:$H$21,"*Stanek*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F41" s="104">
         <f>COUNTIF($I$5:$N$21,"*Stanek*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G41" s="104">
         <f>COUNTIF($O$5:$V$21,"*Stanek*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H41" s="104">
         <f>COUNTIF($C$5:$D$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I41" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -29626,23 +29626,23 @@
       </c>
       <c r="E42" s="104">
         <f>COUNTIF($E$5:$H$21,"*Strand*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F42" s="104">
         <f>COUNTIF($I$5:$N$21,"*Strand*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="G42" s="104">
         <f>COUNTIF($O$5:$V$21,"*Strand*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H42" s="104">
         <f>COUNTIF($C$5:$D$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I42" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -29653,23 +29653,23 @@
       </c>
       <c r="E43" s="104">
         <f>COUNTIF($E$5:$H$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F43" s="104">
         <f>COUNTIF($I$5:$N$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G43" s="104">
         <f>COUNTIF($O$5:$V$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H43" s="104">
         <f>COUNTIF($C$5:$D$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I43" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -29688,23 +29688,23 @@
       </c>
       <c r="E45" s="106">
         <f>COUNTIF($E$5:$H$21,"*Beutel*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F45" s="106">
         <f>COUNTIF($I$5:$N$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G45" s="106">
         <f>COUNTIF($O$5:$V$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H45" s="106">
         <f>COUNTIF($C$5:$D$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I45" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -29715,23 +29715,23 @@
       </c>
       <c r="E46" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F46" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bottke*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G46" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H46" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I46" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -29742,23 +29742,23 @@
       </c>
       <c r="E47" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F47" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G47" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H47" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I47" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -29769,23 +29769,23 @@
       </c>
       <c r="E48" s="106">
         <f>COUNTIF($E$5:$H$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F48" s="106">
         <f>COUNTIF($I$5:$N$21,"*Gaspar*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G48" s="106">
         <f>COUNTIF($O$5:$V$21,"*Gaspar*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H48" s="106">
         <f>COUNTIF($C$5:$D$21,"*Gaspar*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I48" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -29796,23 +29796,23 @@
       </c>
       <c r="E49" s="106">
         <f>COUNTIF($E$5:$H$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F49" s="106">
         <f>COUNTIF($I$5:$N$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G49" s="106">
         <f>COUNTIF($O$5:$V$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H49" s="106">
         <f>COUNTIF($C$5:$D$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I49" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -29823,23 +29823,23 @@
       </c>
       <c r="E50" s="106">
         <f>COUNTIF($E$5:$H$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F50" s="106">
         <f>COUNTIF($I$5:$N$21,"*Patel*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G50" s="106">
         <f>COUNTIF($O$5:$V$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H50" s="106">
         <f>COUNTIF($C$5:$D$21,"*Patel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I50" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -29850,23 +29850,23 @@
       </c>
       <c r="E51" s="106">
         <f>COUNTIF($E$5:$H$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F51" s="106">
         <f>COUNTIF($I$5:$N$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G51" s="106">
         <f>COUNTIF($O$5:$V$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H51" s="106">
         <f>COUNTIF($C$5:$D$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I51" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -29885,23 +29885,23 @@
       </c>
       <c r="E53" s="107">
         <f>COUNTIF($E$5:$H$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F53" s="107">
         <f>COUNTIF($I$5:$N$21,"*Johnson*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G53" s="107">
         <f>COUNTIF($O$5:$V$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H53" s="107">
         <f>COUNTIF($C$5:$D$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I53" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -29912,23 +29912,23 @@
       </c>
       <c r="E54" s="107">
         <f>COUNTIF($E$5:$H$21,"*Lux*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F54" s="107">
         <f>COUNTIF($I$5:$N$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G54" s="107">
         <f>COUNTIF($O$5:$V$21,"*Lux*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H54" s="107">
         <f>COUNTIF($C$5:$D$21,"*Lux*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I54" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -29939,23 +29939,23 @@
       </c>
       <c r="E55" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mautino*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F55" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G55" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mautino*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H55" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I55" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -29966,45 +29966,45 @@
       </c>
       <c r="E56" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mudondo*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F56" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G56" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H56" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I56" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="E57" s="95">
         <f>SUM(E38:E56)</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="F57" s="95">
         <f>SUM(F38:F56)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="G57" s="95">
         <f>SUM(G38:G56)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="H57" s="95">
         <f>SUM(H38:H56)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="I57" s="95">
         <f>SUM(I38:I56)</f>
-        <v/>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -30801,31 +30801,31 @@
       <c r="AG6" s="205" t="n"/>
       <c r="AH6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AI6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AJ6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AL6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AM6" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AN6" s="92">
         <f>SUM(AH6:AM6)</f>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="7" ht="9.949999999999999" customHeight="1">
@@ -31009,35 +31009,35 @@
       <c r="AG9" s="205" t="n"/>
       <c r="AH9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AJ9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AL9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AM9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AN9" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AO9" s="92">
         <f>SUM(AH9:AN9)</f>
-        <v/>
+        <v>20</v>
       </c>
     </row>
     <row r="10" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -31220,23 +31220,23 @@
       <c r="AG12" s="205" t="n"/>
       <c r="AH12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AI12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AJ12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AK12" s="94">
         <f>COUNTIF($C$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AL12" s="84">
         <f>SUM(AH12:AK12)</f>
-        <v/>
+        <v>11</v>
       </c>
     </row>
     <row r="13" ht="9.949999999999999" customFormat="1" customHeight="1" s="41">
@@ -32309,23 +32309,23 @@
       </c>
       <c r="E38" s="104">
         <f>COUNTIF($E$5:$H$21,"*Hard*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F38" s="104">
         <f>COUNTIF($I$5:$N$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G38" s="104">
         <f>COUNTIF($O$5:$V$21,"*Hard*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="H38" s="104">
         <f>COUNTIF($C$5:$D$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I38" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Hard*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -32336,23 +32336,23 @@
       </c>
       <c r="E39" s="104">
         <f>COUNTIF($E$5:$H$21,"*Oehm*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F39" s="104">
         <f>COUNTIF($I$5:$N$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G39" s="104">
         <f>COUNTIF($O$5:$V$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H39" s="104">
         <f>COUNTIF($C$5:$D$21,"*Oehm*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I39" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Oehm*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -32363,23 +32363,23 @@
       </c>
       <c r="E40" s="104">
         <f>COUNTIF($E$5:$H$21,"*Schutt*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F40" s="104">
         <f>COUNTIF($I$5:$N$21,"*Schutt*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G40" s="104">
         <f>COUNTIF($O$5:$V$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H40" s="104">
         <f>COUNTIF($C$5:$D$21,"*Schutt*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I40" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Schutt*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -32390,23 +32390,23 @@
       </c>
       <c r="E41" s="104">
         <f>COUNTIF($E$5:$H$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F41" s="104">
         <f>COUNTIF($I$5:$N$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G41" s="104">
         <f>COUNTIF($O$5:$V$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H41" s="104">
         <f>COUNTIF($C$5:$D$21,"*Stanek*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I41" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Stanek*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -32417,23 +32417,23 @@
       </c>
       <c r="E42" s="104">
         <f>COUNTIF($E$5:$H$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F42" s="104">
         <f>COUNTIF($I$5:$N$21,"*Strand*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="G42" s="104">
         <f>COUNTIF($O$5:$V$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H42" s="104">
         <f>COUNTIF($C$5:$D$21,"*Strand*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I42" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Strand*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -32444,23 +32444,23 @@
       </c>
       <c r="E43" s="104">
         <f>COUNTIF($E$5:$H$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F43" s="104">
         <f>COUNTIF($I$5:$N$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G43" s="104">
         <f>COUNTIF($O$5:$V$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H43" s="104">
         <f>COUNTIF($C$5:$D$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I43" s="104">
         <f>COUNTIF($W$5:$AD$21,"*Wohlgemuth*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -32479,23 +32479,23 @@
       </c>
       <c r="E45" s="106">
         <f>COUNTIF($E$5:$H$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F45" s="106">
         <f>COUNTIF($I$5:$N$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G45" s="106">
         <f>COUNTIF($O$5:$V$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H45" s="106">
         <f>COUNTIF($C$5:$D$21,"*Beutel*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I45" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Beutel*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -32506,23 +32506,23 @@
       </c>
       <c r="E46" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F46" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G46" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H46" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bottke*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I46" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bottke*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -32533,23 +32533,23 @@
       </c>
       <c r="E47" s="106">
         <f>COUNTIF($E$5:$H$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F47" s="106">
         <f>COUNTIF($I$5:$N$21,"*Bower*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G47" s="106">
         <f>COUNTIF($O$5:$V$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H47" s="106">
         <f>COUNTIF($C$5:$D$21,"*Bower*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I47" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Bower*")</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -32560,23 +32560,23 @@
       </c>
       <c r="E48" s="106">
         <f>COUNTIF($E$5:$H$21,"*Gaspar*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F48" s="106">
         <f>COUNTIF($I$5:$N$21,"*Gaspar*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G48" s="106">
         <f>COUNTIF($O$5:$V$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H48" s="106">
         <f>COUNTIF($C$5:$D$21,"*Gaspar*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I48" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Gaspar*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -32587,23 +32587,23 @@
       </c>
       <c r="E49" s="106">
         <f>COUNTIF($E$5:$H$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F49" s="106">
         <f>COUNTIF($I$5:$N$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G49" s="106">
         <f>COUNTIF($O$5:$V$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H49" s="106">
         <f>COUNTIF($C$5:$D$21,"*Kendrick*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I49" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Kendrick*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -32614,23 +32614,23 @@
       </c>
       <c r="E50" s="106">
         <f>COUNTIF($E$5:$H$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F50" s="106">
         <f>COUNTIF($I$5:$N$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G50" s="106">
         <f>COUNTIF($O$5:$V$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H50" s="106">
         <f>COUNTIF($C$5:$D$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I50" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Patel*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -32641,23 +32641,23 @@
       </c>
       <c r="E51" s="106">
         <f>COUNTIF($E$5:$H$21,"*Sublette*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F51" s="106">
         <f>COUNTIF($I$5:$N$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G51" s="106">
         <f>COUNTIF($O$5:$V$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H51" s="106">
         <f>COUNTIF($C$5:$D$21,"*Sublette*")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I51" s="106">
         <f>COUNTIF($W$5:$AD$21,"*Sublette*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -32676,23 +32676,23 @@
       </c>
       <c r="E53" s="107">
         <f>COUNTIF($E$5:$H$21,"*Johnson*")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F53" s="107">
         <f>COUNTIF($I$5:$N$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G53" s="107">
         <f>COUNTIF($O$5:$V$21,"*Johnson*")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="H53" s="107">
         <f>COUNTIF($C$5:$D$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I53" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Johnson*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -32703,23 +32703,23 @@
       </c>
       <c r="E54" s="107">
         <f>COUNTIF($E$5:$H$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F54" s="107">
         <f>COUNTIF($I$5:$N$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G54" s="107">
         <f>COUNTIF($O$5:$V$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H54" s="107">
         <f>COUNTIF($C$5:$D$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I54" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Lux*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -32730,23 +32730,23 @@
       </c>
       <c r="E55" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F55" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mautino*")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="G55" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H55" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I55" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mautino*")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -32757,45 +32757,45 @@
       </c>
       <c r="E56" s="107">
         <f>COUNTIF($E$5:$H$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F56" s="107">
         <f>COUNTIF($I$5:$N$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G56" s="107">
         <f>COUNTIF($O$5:$V$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H56" s="107">
         <f>COUNTIF($C$5:$D$21,"*Mudondo*")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I56" s="107">
         <f>COUNTIF($W$5:$AD$21,"*Mudondo*")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="E57" s="95">
         <f>SUM(E38:E56)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="F57" s="95">
         <f>SUM(F38:F56)</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="G57" s="95">
         <f>SUM(G38:G56)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="H57" s="95">
         <f>SUM(H38:H56)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="I57" s="95">
         <f>SUM(I38:I56)</f>
-        <v/>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
